--- a/outputs/ton_rollover_model/TON_rolling_position_calculator.xlsx
+++ b/outputs/ton_rollover_model/TON_rolling_position_calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victorsim/Desktop/Projects/learn_more_v1.0/outputs/ton_rollover_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A703F0-2484-8443-9B13-065224DC05C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7A17C04-F8C1-CB4D-BD7F-21542961196A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19740" yWindow="500" windowWidth="18660" windowHeight="21100" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,6 +24,7 @@
     <sheet name="检查" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1086,6 +1087,9 @@
     <xf numFmtId="172" fontId="5" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1124,9 +1128,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2066,18 +2067,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -2090,18 +2091,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -2136,20 +2137,20 @@
       <c r="T3" s="5"/>
     </row>
     <row r="4" spans="1:20" ht="20" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="69"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2176,13 +2177,13 @@
         <v>6</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="77">
+      <c r="F5" s="57">
         <v>1</v>
       </c>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -2209,11 +2210,11 @@
         <v>9</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="62"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -2240,11 +2241,11 @@
         <v>11</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -2271,11 +2272,11 @@
         <v>14</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="62"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -2302,11 +2303,11 @@
         <v>16</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="61"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -2333,11 +2334,11 @@
         <v>18</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="61"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -2364,11 +2365,11 @@
         <v>11</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="64"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -3175,36 +3176,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="4" t="s">
@@ -3531,18 +3532,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -3555,18 +3556,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -3601,12 +3602,12 @@
       <c r="T3" s="5"/>
     </row>
     <row r="4" spans="1:20" ht="20" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4397,12 +4398,12 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="1:20" ht="20" customHeight="1">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="68"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -4665,18 +4666,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -4689,18 +4690,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -6906,18 +6907,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -6930,18 +6931,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -9295,18 +9296,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -9319,18 +9320,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -10417,139 +10418,139 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="1:20" ht="20" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="67"/>
-      <c r="R19" s="67"/>
-      <c r="S19" s="68"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="69"/>
       <c r="T19" s="5"/>
     </row>
     <row r="20" spans="1:20" ht="20" customHeight="1">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="59"/>
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="1:20" ht="20" customHeight="1">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="61"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61"/>
+      <c r="S21" s="62"/>
       <c r="T21" s="5"/>
     </row>
     <row r="22" spans="1:20" ht="20" customHeight="1">
-      <c r="A22" s="59"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="61"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="62"/>
       <c r="T22" s="5"/>
     </row>
     <row r="23" spans="1:20" ht="20" customHeight="1">
-      <c r="A23" s="59"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="61"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="62"/>
       <c r="T23" s="5"/>
     </row>
     <row r="24" spans="1:20" ht="20" customHeight="1">
-      <c r="A24" s="62"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="64"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="64"/>
+      <c r="S24" s="65"/>
       <c r="T24" s="5"/>
     </row>
     <row r="25" spans="1:20" ht="20" customHeight="1">
@@ -10940,40 +10941,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
     </row>
     <row r="2" spans="1:14" ht="21" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
     </row>
     <row r="3" spans="1:14" ht="21" customHeight="1"/>
     <row r="4" spans="1:14" ht="21" customHeight="1">
@@ -11683,94 +11684,94 @@
     <row r="17" spans="1:14" ht="21" customHeight="1"/>
     <row r="18" spans="1:14" ht="21" customHeight="1"/>
     <row r="19" spans="1:14" ht="21" customHeight="1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="77" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="68"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="69"/>
     </row>
     <row r="20" spans="1:14" ht="21" customHeight="1">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="75" t="s">
         <v>182</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="68"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="69"/>
     </row>
     <row r="21" spans="1:14" ht="21" customHeight="1">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="68"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="69"/>
     </row>
     <row r="22" spans="1:14" ht="21" customHeight="1">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="75" t="s">
         <v>184</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
     </row>
     <row r="23" spans="1:14" ht="21" customHeight="1">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -11798,18 +11799,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -11822,18 +11823,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -13059,18 +13060,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -13083,18 +13084,18 @@
       <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -13742,7 +13743,6 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
